--- a/example/excel/common.xlsx
+++ b/example/excel/common.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -630,6 +630,23 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>掉落数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>int?=1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>权重(可选,省略时取默认值1)</t>
         </is>
       </c>
     </row>
